--- a/activity/M01A00/M01A00.xlsx
+++ b/activity/M01A00/M01A00.xlsx
@@ -8,17 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A00\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36AE1256-F529-48BD-AB70-34D72DD08011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B3694B-CDC3-44A2-9490-D2476DDA4D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="773" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-28898" yWindow="6562" windowWidth="28996" windowHeight="15675" tabRatio="773" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="13" r:id="rId1"/>
     <sheet name="RealineamientoReportado" sheetId="12" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Calificacion!$B$2:$F$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">RealineamientoReportado!$B$2:$D$14</definedName>
@@ -498,7 +495,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -554,104 +551,101 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1705,75 +1699,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Calificacion"/>
-      <sheetName val="Detalle"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2" t="str">
-            <v>Calificación: 1.2. Modelación hidrológica para obtención de caudales de diseño e hidrogramas para tránsito de crecientes</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="F4" t="str">
-            <v>Calificación final</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>Grupo 1</v>
-          </cell>
-          <cell r="F5">
-            <v>4.5</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>Grupo 2</v>
-          </cell>
-          <cell r="F6">
-            <v>4.5</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>Grupo 3</v>
-          </cell>
-          <cell r="F7">
-            <v>4.95</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>Grupo 4</v>
-          </cell>
-          <cell r="F8">
-            <v>4.5999999999999996</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>Grupo 5</v>
-          </cell>
-          <cell r="F9">
-            <v>1.5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -2074,270 +1999,270 @@
   <dimension ref="B1:F20"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" style="26" customWidth="1"/>
-    <col min="3" max="4" width="11.46484375" style="26" customWidth="1"/>
-    <col min="5" max="5" width="12.796875" style="26" customWidth="1"/>
-    <col min="6" max="6" width="11.46484375" style="26" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="26" customWidth="1"/>
-    <col min="8" max="16384" width="11.33203125" style="26"/>
+    <col min="1" max="1" width="2.6640625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="19" customWidth="1"/>
+    <col min="3" max="4" width="11.46484375" style="19" customWidth="1"/>
+    <col min="5" max="5" width="12.796875" style="19" customWidth="1"/>
+    <col min="6" max="6" width="11.46484375" style="19" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="19" customWidth="1"/>
+    <col min="8" max="16384" width="11.33203125" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="43" t="s">
+      <c r="F1" s="31" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
     </row>
     <row r="4" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="22" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="25">
         <v>5</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="24">
         <f>RealineamientoReportado!E12</f>
         <v>0</v>
       </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="35">
+      <c r="E5" s="25"/>
+      <c r="F5" s="26">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="25">
         <v>5</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="24">
         <f>RealineamientoReportado!G12</f>
         <v>0</v>
       </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35">
+      <c r="E6" s="25"/>
+      <c r="F6" s="26">
         <f t="shared" ref="F6:F17" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="25">
         <v>5</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="24">
         <f>RealineamientoReportado!I12</f>
         <v>0</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="35">
+      <c r="E7" s="25"/>
+      <c r="F7" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="25">
         <v>5</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="24">
         <f>RealineamientoReportado!K12</f>
         <v>0</v>
       </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="35">
+      <c r="E8" s="25"/>
+      <c r="F8" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="25">
         <v>5</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="24">
         <f>RealineamientoReportado!M12</f>
         <v>0</v>
       </c>
-      <c r="E9" s="34"/>
-      <c r="F9" s="35">
+      <c r="E9" s="25"/>
+      <c r="F9" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="25">
         <v>5</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="24">
         <f>RealineamientoReportado!O12</f>
         <v>0</v>
       </c>
-      <c r="E10" s="34"/>
-      <c r="F10" s="35">
+      <c r="E10" s="25"/>
+      <c r="F10" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="25">
         <v>5</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="24">
         <f>RealineamientoReportado!Q12</f>
         <v>0</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="35">
+      <c r="E11" s="25"/>
+      <c r="F11" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="25">
         <v>5</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="24">
         <f>RealineamientoReportado!S12</f>
         <v>0</v>
       </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="35">
+      <c r="E12" s="25"/>
+      <c r="F12" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="25">
         <v>5</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="24">
         <f>RealineamientoReportado!U12</f>
         <v>0</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="35">
+      <c r="E13" s="25"/>
+      <c r="F13" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="25">
         <v>5</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="24">
         <f>RealineamientoReportado!W12</f>
         <v>0</v>
       </c>
-      <c r="E14" s="34"/>
-      <c r="F14" s="35">
+      <c r="E14" s="25"/>
+      <c r="F14" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="25">
         <v>5</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="24">
         <f>RealineamientoReportado!Y12</f>
         <v>0</v>
       </c>
-      <c r="E15" s="34"/>
-      <c r="F15" s="35">
+      <c r="E15" s="25"/>
+      <c r="F15" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="25">
         <v>5</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="24">
         <f>RealineamientoReportado!AA12</f>
         <v>0</v>
       </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="35">
+      <c r="E16" s="25"/>
+      <c r="F16" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="29">
         <v>5</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="28">
         <f>RealineamientoReportado!AC12</f>
         <v>0</v>
       </c>
-      <c r="E17" s="39"/>
-      <c r="F17" s="35">
+      <c r="E17" s="29"/>
+      <c r="F17" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2352,18 +2277,18 @@
       <c r="F18" s="40"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2418,12 +2343,12 @@
     <col min="31" max="16384" width="11.3984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="45" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="44"/>
-      <c r="B1" s="44" t="s">
+    <row r="1" spans="1:30" s="33" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="32"/>
+      <c r="B1" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="46"/>
+      <c r="D1" s="34"/>
       <c r="E1" s="14"/>
       <c r="G1" s="14"/>
       <c r="I1" s="14"/>
@@ -2439,74 +2364,74 @@
       <c r="AC1" s="14"/>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B2" s="49"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="20" t="str">
+      <c r="B2" s="35"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="44" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="20" t="str">
+      <c r="F2" s="45"/>
+      <c r="G2" s="44" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="H2" s="21"/>
-      <c r="I2" s="20" t="str">
+      <c r="H2" s="45"/>
+      <c r="I2" s="44" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="21"/>
-      <c r="K2" s="42" t="str">
+      <c r="J2" s="45"/>
+      <c r="K2" s="46" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="20" t="str">
+      <c r="L2" s="45"/>
+      <c r="M2" s="44" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="N2" s="21"/>
-      <c r="O2" s="20" t="str">
+      <c r="N2" s="45"/>
+      <c r="O2" s="44" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="20" t="str">
+      <c r="P2" s="45"/>
+      <c r="Q2" s="44" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="R2" s="21"/>
-      <c r="S2" s="20" t="str">
+      <c r="R2" s="45"/>
+      <c r="S2" s="44" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="T2" s="21"/>
-      <c r="U2" s="20" t="str">
+      <c r="T2" s="45"/>
+      <c r="U2" s="44" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="V2" s="21"/>
-      <c r="W2" s="20" t="str">
+      <c r="V2" s="45"/>
+      <c r="W2" s="44" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="20" t="str">
+      <c r="X2" s="45"/>
+      <c r="Y2" s="44" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="20" t="str">
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="44" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="20" t="str">
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="44" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AD2" s="21"/>
+      <c r="AD2" s="45"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.45">
       <c r="B3" s="4" t="s">
@@ -2598,7 +2523,7 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="43" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -2661,7 +2586,7 @@
       <c r="AD4" s="6"/>
     </row>
     <row r="5" spans="1:30" ht="33" x14ac:dyDescent="0.45">
-      <c r="B5" s="23"/>
+      <c r="B5" s="43"/>
       <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
@@ -2696,7 +2621,7 @@
       <c r="AD5" s="6"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B6" s="23"/>
+      <c r="B6" s="43"/>
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
@@ -2731,7 +2656,7 @@
       <c r="AD6" s="6"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B7" s="23"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
@@ -2766,7 +2691,7 @@
       <c r="AD7" s="6"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B8" s="23"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
@@ -2801,7 +2726,7 @@
       <c r="AD8" s="6"/>
     </row>
     <row r="9" spans="1:30" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="23"/>
+      <c r="B9" s="43"/>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
@@ -2836,7 +2761,7 @@
       <c r="AD9" s="6"/>
     </row>
     <row r="10" spans="1:30" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="23"/>
+      <c r="B10" s="43"/>
       <c r="C10" s="3" t="s">
         <v>20</v>
       </c>
@@ -2902,86 +2827,86 @@
       <c r="AD11" s="8"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="48">
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="42">
         <f>AVERAGE(E4:E11)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48">
+      <c r="F12" s="42"/>
+      <c r="G12" s="42">
         <f>AVERAGE(G4:G11)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48">
+      <c r="H12" s="42"/>
+      <c r="I12" s="42">
         <f>AVERAGE(I4:I11)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48">
+      <c r="J12" s="42"/>
+      <c r="K12" s="42">
         <f>AVERAGE(K4:K11)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48">
+      <c r="L12" s="42"/>
+      <c r="M12" s="42">
         <f>AVERAGE(M4:M11)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="48"/>
-      <c r="O12" s="48">
+      <c r="N12" s="42"/>
+      <c r="O12" s="42">
         <f>AVERAGE(O4:O11)</f>
         <v>0</v>
       </c>
-      <c r="P12" s="48"/>
-      <c r="Q12" s="48">
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42">
         <f>AVERAGE(Q4:Q11)</f>
         <v>0</v>
       </c>
-      <c r="R12" s="48"/>
-      <c r="S12" s="48">
+      <c r="R12" s="42"/>
+      <c r="S12" s="42">
         <f>AVERAGE(S4:S11)</f>
         <v>0</v>
       </c>
-      <c r="T12" s="48"/>
-      <c r="U12" s="48">
+      <c r="T12" s="42"/>
+      <c r="U12" s="42">
         <f>AVERAGE(U4:U11)</f>
         <v>0</v>
       </c>
-      <c r="V12" s="48"/>
-      <c r="W12" s="48">
+      <c r="V12" s="42"/>
+      <c r="W12" s="42">
         <f>AVERAGE(W4:W11)</f>
         <v>0</v>
       </c>
-      <c r="X12" s="48"/>
-      <c r="Y12" s="48">
+      <c r="X12" s="42"/>
+      <c r="Y12" s="42">
         <f>AVERAGE(Y4:Y11)</f>
         <v>0</v>
       </c>
-      <c r="Z12" s="48"/>
-      <c r="AA12" s="48">
+      <c r="Z12" s="42"/>
+      <c r="AA12" s="42">
         <f>AVERAGE(AA4:AA11)</f>
         <v>0</v>
       </c>
-      <c r="AB12" s="48"/>
-      <c r="AC12" s="48">
+      <c r="AB12" s="42"/>
+      <c r="AC12" s="42">
         <f>AVERAGE(AC4:AC11)</f>
         <v>0</v>
       </c>
-      <c r="AD12" s="48"/>
+      <c r="AD12" s="42"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B13" s="24"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
     </row>
     <row r="22" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C22" s="2"/>
@@ -3033,6 +2958,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="W12:X12"/>
     <mergeCell ref="Y12:Z12"/>
     <mergeCell ref="AA12:AB12"/>
     <mergeCell ref="AC12:AD12"/>
@@ -3049,19 +2987,6 @@
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="O2:P2"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="W12:X12"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/activity/M01A00/M01A00.xlsx
+++ b/activity/M01A00/M01A00.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A00\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B3694B-CDC3-44A2-9490-D2476DDA4D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC721947-ABD1-472A-98E3-3F87AF5FA292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="6562" windowWidth="28996" windowHeight="15675" tabRatio="773" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="773" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="13" r:id="rId1"/>
     <sheet name="RealineamientoReportado" sheetId="12" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Calificacion!$B$2:$F$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Calificacion!$B$2:$F$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">RealineamientoReportado!$B$2:$D$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">RealineamientoReportado!$2:$3</definedName>
   </definedNames>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
   <si>
     <t>Tipo</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t>Grupo 13</t>
+  </si>
+  <si>
+    <t>Grupo 14</t>
   </si>
 </sst>
 </file>
@@ -273,7 +276,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -486,6 +489,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -495,7 +511,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -608,6 +624,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -620,31 +639,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1996,7 +2018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6764DDA9-ACBF-4BC2-8821-9CA07B4AA378}">
-  <dimension ref="B1:F20"/>
+  <dimension ref="B1:F21"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="19" customWidth="1"/>
@@ -2014,20 +2036,20 @@
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="20" t="s">
@@ -2076,7 +2098,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="26">
-        <f t="shared" ref="F6:F17" si="0">AVERAGE(D6:E6)</f>
+        <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
       </c>
     </row>
@@ -2251,53 +2273,70 @@
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="25">
         <v>5</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="52">
         <f>RealineamientoReportado!AC12</f>
         <v>0</v>
       </c>
-      <c r="E17" s="29"/>
-      <c r="F17" s="50">
+      <c r="E17" s="51"/>
+      <c r="F17" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="40" t="s">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B18" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="29">
+        <v>5</v>
+      </c>
+      <c r="D18" s="28">
+        <f>RealineamientoReportado!AE12</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="29"/>
+      <c r="F18" s="38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B19" s="41"/>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
       <c r="E19" s="41"/>
       <c r="F19" s="41"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:F3"/>
-    <mergeCell ref="B18:F19"/>
+    <mergeCell ref="B19:F20"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B18" r:id="rId1" xr:uid="{B1817C3D-E587-407A-8D66-AAA0AD88E73B}"/>
+    <hyperlink ref="B19" r:id="rId1" xr:uid="{B1817C3D-E587-407A-8D66-AAA0AD88E73B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -2307,7 +2346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6131B6-D0CB-405A-ABA0-C146745C9D16}">
-  <dimension ref="A1:AD37"/>
+  <dimension ref="A1:AF37"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -2340,10 +2379,12 @@
     <col min="28" max="28" width="30.6640625" style="2" customWidth="1"/>
     <col min="29" max="29" width="5.6640625" style="2" customWidth="1"/>
     <col min="30" max="30" width="30.6640625" style="2" customWidth="1"/>
-    <col min="31" max="16384" width="11.3984375" style="2"/>
+    <col min="31" max="31" width="5.6640625" style="2" customWidth="1"/>
+    <col min="32" max="32" width="30.6640625" style="2" customWidth="1"/>
+    <col min="33" max="16384" width="11.3984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="33" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:32" s="33" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A1" s="32"/>
       <c r="B1" s="32" t="s">
         <v>33</v>
@@ -2362,78 +2403,84 @@
       <c r="Y1" s="14"/>
       <c r="AA1" s="14"/>
       <c r="AC1" s="14"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="AE1" s="14"/>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="B2" s="35"/>
       <c r="C2" s="36"/>
       <c r="D2" s="37"/>
-      <c r="E2" s="44" t="str">
+      <c r="E2" s="45" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="F2" s="45"/>
-      <c r="G2" s="44" t="str">
+      <c r="F2" s="46"/>
+      <c r="G2" s="45" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="H2" s="45"/>
-      <c r="I2" s="44" t="str">
+      <c r="H2" s="46"/>
+      <c r="I2" s="45" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="45"/>
-      <c r="K2" s="46" t="str">
+      <c r="J2" s="46"/>
+      <c r="K2" s="50" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="L2" s="45"/>
-      <c r="M2" s="44" t="str">
+      <c r="L2" s="46"/>
+      <c r="M2" s="45" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="N2" s="45"/>
-      <c r="O2" s="44" t="str">
+      <c r="N2" s="46"/>
+      <c r="O2" s="45" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="44" t="str">
+      <c r="P2" s="46"/>
+      <c r="Q2" s="45" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="R2" s="45"/>
-      <c r="S2" s="44" t="str">
+      <c r="R2" s="46"/>
+      <c r="S2" s="45" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="T2" s="45"/>
-      <c r="U2" s="44" t="str">
+      <c r="T2" s="46"/>
+      <c r="U2" s="45" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="V2" s="45"/>
-      <c r="W2" s="44" t="str">
+      <c r="V2" s="46"/>
+      <c r="W2" s="45" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="X2" s="45"/>
-      <c r="Y2" s="44" t="str">
+      <c r="X2" s="46"/>
+      <c r="Y2" s="45" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="Z2" s="45"/>
-      <c r="AA2" s="44" t="str">
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="45" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AB2" s="45"/>
-      <c r="AC2" s="44" t="str">
+      <c r="AB2" s="46"/>
+      <c r="AC2" s="45" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AD2" s="45"/>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="AD2" s="46"/>
+      <c r="AE2" s="45" t="str">
+        <f>Calificacion!B18</f>
+        <v>Grupo 14</v>
+      </c>
+      <c r="AF2" s="46"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
@@ -2521,9 +2568,15 @@
       <c r="AD3" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B4" s="43" t="s">
+      <c r="AE3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B4" s="49" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -2584,9 +2637,13 @@
         <v>0</v>
       </c>
       <c r="AD4" s="6"/>
-    </row>
-    <row r="5" spans="1:30" ht="33" x14ac:dyDescent="0.45">
-      <c r="B5" s="43"/>
+      <c r="AE4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="6"/>
+    </row>
+    <row r="5" spans="1:32" ht="33" x14ac:dyDescent="0.45">
+      <c r="B5" s="49"/>
       <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
@@ -2619,9 +2676,11 @@
       <c r="AB5" s="6"/>
       <c r="AC5" s="10"/>
       <c r="AD5" s="6"/>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B6" s="43"/>
+      <c r="AE5" s="10"/>
+      <c r="AF5" s="6"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B6" s="49"/>
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
@@ -2654,9 +2713,11 @@
       <c r="AB6" s="6"/>
       <c r="AC6" s="10"/>
       <c r="AD6" s="6"/>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B7" s="43"/>
+      <c r="AE6" s="10"/>
+      <c r="AF6" s="6"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B7" s="49"/>
       <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
@@ -2689,9 +2750,11 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="10"/>
       <c r="AD7" s="6"/>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B8" s="43"/>
+      <c r="AE7" s="10"/>
+      <c r="AF7" s="6"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B8" s="49"/>
       <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
@@ -2724,9 +2787,11 @@
       <c r="AB8" s="6"/>
       <c r="AC8" s="10"/>
       <c r="AD8" s="6"/>
-    </row>
-    <row r="9" spans="1:30" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="43"/>
+      <c r="AE8" s="10"/>
+      <c r="AF8" s="6"/>
+    </row>
+    <row r="9" spans="1:32" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="49"/>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
@@ -2759,9 +2824,11 @@
       <c r="AB9" s="6"/>
       <c r="AC9" s="10"/>
       <c r="AD9" s="6"/>
-    </row>
-    <row r="10" spans="1:30" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="43"/>
+      <c r="AE9" s="10"/>
+      <c r="AF9" s="6"/>
+    </row>
+    <row r="10" spans="1:32" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="49"/>
       <c r="C10" s="3" t="s">
         <v>20</v>
       </c>
@@ -2794,8 +2861,10 @@
       <c r="AB10" s="6"/>
       <c r="AC10" s="10"/>
       <c r="AD10" s="6"/>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="6"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
       <c r="B11" s="12"/>
       <c r="C11" s="7"/>
       <c r="D11" s="18"/>
@@ -2825,88 +2894,95 @@
       <c r="AB11" s="8"/>
       <c r="AC11" s="11"/>
       <c r="AD11" s="8"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B12" s="49" t="s">
+      <c r="AE11" s="11"/>
+      <c r="AF11" s="8"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B12" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="42">
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="48">
         <f>AVERAGE(E4:E11)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42">
+      <c r="F12" s="48"/>
+      <c r="G12" s="48">
         <f>AVERAGE(G4:G11)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42">
+      <c r="H12" s="48"/>
+      <c r="I12" s="48">
         <f>AVERAGE(I4:I11)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42">
+      <c r="J12" s="48"/>
+      <c r="K12" s="48">
         <f>AVERAGE(K4:K11)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42">
+      <c r="L12" s="48"/>
+      <c r="M12" s="48">
         <f>AVERAGE(M4:M11)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42">
+      <c r="N12" s="48"/>
+      <c r="O12" s="48">
         <f>AVERAGE(O4:O11)</f>
         <v>0</v>
       </c>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42">
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48">
         <f>AVERAGE(Q4:Q11)</f>
         <v>0</v>
       </c>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42">
+      <c r="R12" s="48"/>
+      <c r="S12" s="48">
         <f>AVERAGE(S4:S11)</f>
         <v>0</v>
       </c>
-      <c r="T12" s="42"/>
-      <c r="U12" s="42">
+      <c r="T12" s="48"/>
+      <c r="U12" s="48">
         <f>AVERAGE(U4:U11)</f>
         <v>0</v>
       </c>
-      <c r="V12" s="42"/>
-      <c r="W12" s="42">
+      <c r="V12" s="48"/>
+      <c r="W12" s="48">
         <f>AVERAGE(W4:W11)</f>
         <v>0</v>
       </c>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="42">
+      <c r="X12" s="48"/>
+      <c r="Y12" s="48">
         <f>AVERAGE(Y4:Y11)</f>
         <v>0</v>
       </c>
-      <c r="Z12" s="42"/>
-      <c r="AA12" s="42">
+      <c r="Z12" s="48"/>
+      <c r="AA12" s="48">
         <f>AVERAGE(AA4:AA11)</f>
         <v>0</v>
       </c>
-      <c r="AB12" s="42"/>
-      <c r="AC12" s="42">
+      <c r="AB12" s="48"/>
+      <c r="AC12" s="48">
         <f>AVERAGE(AC4:AC11)</f>
         <v>0</v>
       </c>
-      <c r="AD12" s="42"/>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B13" s="47"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
+      <c r="AD12" s="48"/>
+      <c r="AE12" s="48">
+        <f>AVERAGE(AE4:AE11)</f>
+        <v>0</v>
+      </c>
+      <c r="AF12" s="48"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B13" s="43"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
     </row>
     <row r="22" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C22" s="2"/>
@@ -2957,9 +3033,24 @@
       <c r="C37" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="31">
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:X2"/>
     <mergeCell ref="B13:D14"/>
-    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AF2"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="G12:H12"/>
@@ -2973,20 +3064,7 @@
     <mergeCell ref="W12:X12"/>
     <mergeCell ref="Y12:Z12"/>
     <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="B4:B10"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="AE12:AF12"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/activity/M01A00/M01A00.xlsx
+++ b/activity/M01A00/M01A00.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A00\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC721947-ABD1-472A-98E3-3F87AF5FA292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B029C93F-A73B-4991-97C5-28B37D387C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="773" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="773" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
   <si>
     <t>Tipo</t>
   </si>
@@ -112,9 +112,6 @@
   </si>
   <si>
     <t>Calificación final</t>
-  </si>
-  <si>
-    <t>1.0. Investigación de casos de estudio</t>
   </si>
   <si>
     <t>M01A00</t>
@@ -627,6 +624,12 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -639,35 +642,29 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -712,7 +709,7 @@
           <c:strCache>
             <c:ptCount val="1"/>
             <c:pt idx="0">
-              <c:v>1.0. Investigación de casos de estudio</c:v>
+              <c:v>Calificación: 1.0. Investigación de casos de estudio</c:v>
             </c:pt>
           </c:strCache>
         </c:strRef>
@@ -721,8 +718,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11625304490753174"/>
-          <c:y val="9.2445423853441304E-4"/>
+          <c:x val="0.25137410338587657"/>
+          <c:y val="1.7732207079780703E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1683,15 +1680,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>57065</xdr:colOff>
+      <xdr:colOff>57064</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>20836</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>123065</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>78590</xdr:rowOff>
+      <xdr:colOff>149689</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>99726</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2032,24 +2029,24 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
       <c r="F1" s="31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="B2" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
     </row>
     <row r="4" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="20" t="s">
@@ -2155,7 +2152,7 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B10" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="25">
         <v>5</v>
@@ -2172,7 +2169,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B11" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" s="25">
         <v>5</v>
@@ -2189,7 +2186,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="25">
         <v>5</v>
@@ -2206,7 +2203,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B13" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" s="25">
         <v>5</v>
@@ -2223,7 +2220,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B14" s="23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="25">
         <v>5</v>
@@ -2240,7 +2237,7 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B15" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="25">
         <v>5</v>
@@ -2257,7 +2254,7 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B16" s="23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="25">
         <v>5</v>
@@ -2274,16 +2271,16 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" s="25">
         <v>5</v>
       </c>
-      <c r="D17" s="52">
+      <c r="D17" s="40">
         <f>RealineamientoReportado!AC12</f>
         <v>0</v>
       </c>
-      <c r="E17" s="51"/>
+      <c r="E17" s="39"/>
       <c r="F17" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2291,7 +2288,7 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" s="29">
         <v>5</v>
@@ -2307,20 +2304,20 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="30"/>
@@ -2386,8 +2383,9 @@
   <sheetData>
     <row r="1" spans="1:32" s="33" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A1" s="32"/>
-      <c r="B1" s="32" t="s">
-        <v>33</v>
+      <c r="B1" s="32" t="str">
+        <f>Calificacion!B2</f>
+        <v>Calificación: 1.0. Investigación de casos de estudio</v>
       </c>
       <c r="D1" s="34"/>
       <c r="E1" s="14"/>
@@ -2424,7 +2422,7 @@
         <v>Grupo 3</v>
       </c>
       <c r="J2" s="46"/>
-      <c r="K2" s="50" t="str">
+      <c r="K2" s="48" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
@@ -2898,91 +2896,91 @@
       <c r="AF11" s="8"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B12" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="48">
+      <c r="B12" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="47">
         <f>AVERAGE(E4:E11)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48">
+      <c r="F12" s="47"/>
+      <c r="G12" s="47">
         <f>AVERAGE(G4:G11)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48">
+      <c r="H12" s="47"/>
+      <c r="I12" s="47">
         <f>AVERAGE(I4:I11)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48">
+      <c r="J12" s="47"/>
+      <c r="K12" s="47">
         <f>AVERAGE(K4:K11)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48">
+      <c r="L12" s="47"/>
+      <c r="M12" s="47">
         <f>AVERAGE(M4:M11)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="48"/>
-      <c r="O12" s="48">
+      <c r="N12" s="47"/>
+      <c r="O12" s="47">
         <f>AVERAGE(O4:O11)</f>
         <v>0</v>
       </c>
-      <c r="P12" s="48"/>
-      <c r="Q12" s="48">
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47">
         <f>AVERAGE(Q4:Q11)</f>
         <v>0</v>
       </c>
-      <c r="R12" s="48"/>
-      <c r="S12" s="48">
+      <c r="R12" s="47"/>
+      <c r="S12" s="47">
         <f>AVERAGE(S4:S11)</f>
         <v>0</v>
       </c>
-      <c r="T12" s="48"/>
-      <c r="U12" s="48">
+      <c r="T12" s="47"/>
+      <c r="U12" s="47">
         <f>AVERAGE(U4:U11)</f>
         <v>0</v>
       </c>
-      <c r="V12" s="48"/>
-      <c r="W12" s="48">
+      <c r="V12" s="47"/>
+      <c r="W12" s="47">
         <f>AVERAGE(W4:W11)</f>
         <v>0</v>
       </c>
-      <c r="X12" s="48"/>
-      <c r="Y12" s="48">
+      <c r="X12" s="47"/>
+      <c r="Y12" s="47">
         <f>AVERAGE(Y4:Y11)</f>
         <v>0</v>
       </c>
-      <c r="Z12" s="48"/>
-      <c r="AA12" s="48">
+      <c r="Z12" s="47"/>
+      <c r="AA12" s="47">
         <f>AVERAGE(AA4:AA11)</f>
         <v>0</v>
       </c>
-      <c r="AB12" s="48"/>
-      <c r="AC12" s="48">
+      <c r="AB12" s="47"/>
+      <c r="AC12" s="47">
         <f>AVERAGE(AC4:AC11)</f>
         <v>0</v>
       </c>
-      <c r="AD12" s="48"/>
-      <c r="AE12" s="48">
+      <c r="AD12" s="47"/>
+      <c r="AE12" s="47">
         <f>AVERAGE(AE4:AE11)</f>
         <v>0</v>
       </c>
-      <c r="AF12" s="48"/>
+      <c r="AF12" s="47"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B13" s="43"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
     </row>
     <row r="22" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C22" s="2"/>
@@ -3034,21 +3032,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AC12:AD12"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="B4:B10"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
     <mergeCell ref="B13:D14"/>
     <mergeCell ref="AE2:AF2"/>
     <mergeCell ref="B12:D12"/>
@@ -3065,6 +3048,21 @@
     <mergeCell ref="Y12:Z12"/>
     <mergeCell ref="AA12:AB12"/>
     <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
